--- a/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
@@ -37,7 +37,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>Icon</t>
   </si>
   <si>
     <t>AddPropreListStr</t>
@@ -114,6 +117,21 @@
   </si>
   <si>
     <t>寒霜</t>
+  </si>
+  <si>
+    <t>强击2</t>
+  </si>
+  <si>
+    <t>扩域2</t>
+  </si>
+  <si>
+    <t>雷击2</t>
+  </si>
+  <si>
+    <t>灼烧2</t>
+  </si>
+  <si>
+    <t>寒霜2</t>
   </si>
 </sst>
 </file>
@@ -11306,7 +11324,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{E3FA5DA9-829A-4E6A-B191-8DE540D08050}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{31E0C635-3CBF-47EC-B41D-CEC83AD80A53}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11606,15 +11624,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="17.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22" style="3" customWidth="1"/>
-    <col min="4" max="4" width="43.75" style="3" customWidth="1"/>
+    <col min="3" max="4" width="22" style="3" customWidth="1"/>
+    <col min="5" max="5" width="70.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -11627,73 +11645,152 @@
       <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="D2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:4">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="B4" s="2">
         <v>101000111</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1110001</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="B5" s="2">
         <v>101000121</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1110001</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="B6" s="2">
         <v>101000122</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1110001</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="B7" s="2">
         <v>101000131</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1110001</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="B8" s="2">
         <v>101000132</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1110001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="2">
+        <v>101001111</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1120001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="2">
+        <v>101001121</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1120001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="2">
+        <v>101001122</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1120001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="2">
+        <v>101001131</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1120001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="2">
+        <v>101001132</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1120001</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
@@ -11324,7 +11324,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{31E0C635-3CBF-47EC-B41D-CEC83AD80A53}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{722C9E6B-4374-4B96-8EC5-A160513ED2EC}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11702,7 +11702,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="3">
-        <v>1110001</v>
+        <v>2102020</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -11713,7 +11713,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="3">
-        <v>1110001</v>
+        <v>2102010</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -11724,7 +11724,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="3">
-        <v>1110001</v>
+        <v>2200010</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -11735,7 +11735,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="3">
-        <v>1110001</v>
+        <v>1120011</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -11746,7 +11746,7 @@
         <v>16</v>
       </c>
       <c r="D9" s="3">
-        <v>1120001</v>
+        <v>1110001</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -11757,7 +11757,7 @@
         <v>17</v>
       </c>
       <c r="D10" s="3">
-        <v>1120001</v>
+        <v>2102020</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -11768,7 +11768,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="3">
-        <v>1120001</v>
+        <v>2102010</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -11779,7 +11779,7 @@
         <v>19</v>
       </c>
       <c r="D12" s="3">
-        <v>1120001</v>
+        <v>2200010</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -11790,7 +11790,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="3">
-        <v>1120001</v>
+        <v>1120011</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
@@ -37,7 +37,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="F4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Icon</t>
+  </si>
+  <si>
+    <t>Des</t>
   </si>
   <si>
     <t>AddPropreListStr</t>
@@ -95,10 +98,19 @@
     <t>string</t>
   </si>
   <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
     <t>名称</t>
+  </si>
+  <si>
+    <t>描述</t>
   </si>
   <si>
     <t>附加</t>
@@ -107,16 +119,31 @@
     <t>强击</t>
   </si>
   <si>
+    <t>增加伤害</t>
+  </si>
+  <si>
     <t>扩域</t>
+  </si>
+  <si>
+    <t>增大技能范围</t>
   </si>
   <si>
     <t>雷击</t>
   </si>
   <si>
+    <t>命中后电一下</t>
+  </si>
+  <si>
     <t>灼烧</t>
   </si>
   <si>
+    <t>命中后挂个灼烧Buff</t>
+  </si>
+  <si>
     <t>寒霜</t>
+  </si>
+  <si>
+    <t>命中后挂个减速Buff</t>
   </si>
   <si>
     <t>强击2</t>
@@ -11324,7 +11351,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{722C9E6B-4374-4B96-8EC5-A160513ED2EC}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{09E6794B-12F5-430A-8267-CBED78AA5AB5}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11624,15 +11651,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="17.625" style="2" customWidth="1"/>
     <col min="3" max="4" width="22" style="3" customWidth="1"/>
-    <col min="5" max="5" width="70.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23" style="3" customWidth="1"/>
+    <col min="6" max="6" width="70.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -11648,149 +11676,202 @@
       <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="C2" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="D2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:5">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="7"/>
       <c r="D3" s="6" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:5">
-      <c r="B4" s="2">
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="2">
         <v>101000111</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D5" s="3">
         <v>1110001</v>
       </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="B5" s="2">
+    <row r="6" spans="1:6">
+      <c r="B6" s="2">
         <v>101000121</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D6" s="3">
         <v>2102020</v>
       </c>
+      <c r="E6" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="B6" s="2">
+    <row r="7" spans="1:6">
+      <c r="B7" s="2">
         <v>101000122</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D7" s="3">
         <v>2102010</v>
       </c>
+      <c r="E7" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="B7" s="2">
+    <row r="8" spans="1:6">
+      <c r="B8" s="2">
         <v>101000131</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
+      <c r="C8" s="3" t="s">
+        <v>21</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D8" s="3">
         <v>2200010</v>
       </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="B8" s="2">
+    <row r="9" spans="1:6">
+      <c r="B9" s="2">
         <v>101000132</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>15</v>
+      <c r="C9" s="3" t="s">
+        <v>23</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D9" s="3">
         <v>1120011</v>
       </c>
+      <c r="E9" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="B9" s="2">
+    <row r="10" spans="1:6">
+      <c r="B10" s="2">
         <v>101001111</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1110001</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="3">
-        <v>1110001</v>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="2">
+        <v>101001121</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2102020</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="B10" s="2">
-        <v>101001121</v>
+    <row r="12" spans="1:6">
+      <c r="B12" s="2">
+        <v>101001122</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>17</v>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
       </c>
-      <c r="D10" s="3">
-        <v>2102020</v>
+      <c r="D12" s="3">
+        <v>2102010</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="B11" s="2">
-        <v>101001122</v>
+    <row r="13" spans="1:6">
+      <c r="B13" s="2">
+        <v>101001131</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>18</v>
+      <c r="C13" s="3" t="s">
+        <v>28</v>
       </c>
-      <c r="D11" s="3">
-        <v>2102010</v>
+      <c r="D13" s="3">
+        <v>2200010</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="B12" s="2">
-        <v>101001131</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="3">
-        <v>2200010</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="B13" s="2">
+    <row r="14" spans="1:6">
+      <c r="B14" s="2">
         <v>101001132</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>20</v>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D14" s="3">
         <v>1120011</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
@@ -116,12 +116,6 @@
     <t>附加</t>
   </si>
   <si>
-    <t>强击</t>
-  </si>
-  <si>
-    <t>增加伤害</t>
-  </si>
-  <si>
     <t>扩域</t>
   </si>
   <si>
@@ -146,7 +140,10 @@
     <t>命中后挂个减速Buff</t>
   </si>
   <si>
-    <t>强击2</t>
+    <t>恐惧</t>
+  </si>
+  <si>
+    <t>命中后挂个恐惧Buff</t>
   </si>
   <si>
     <t>扩域2</t>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>寒霜2</t>
+  </si>
+  <si>
+    <t>恐惧2</t>
   </si>
 </sst>
 </file>
@@ -11351,7 +11351,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{09E6794B-12F5-430A-8267-CBED78AA5AB5}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{CEB8611B-D2B8-4B50-94D3-A462C68F57CD}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11742,7 +11742,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="3">
-        <v>1110001</v>
+        <v>2102020</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>16</v>
@@ -11750,13 +11750,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="2">
-        <v>101000121</v>
+        <v>101000112</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="3">
-        <v>2102020</v>
+        <v>2102010</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>18</v>
@@ -11764,13 +11764,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="2">
-        <v>101000122</v>
+        <v>101000121</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="3">
-        <v>2102010</v>
+        <v>2200010</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>20</v>
@@ -11778,31 +11778,32 @@
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="2">
-        <v>101000131</v>
+        <v>101000122</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="3">
-        <v>2200010</v>
+        <v>1120011</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" customFormat="1" spans="1:6">
       <c r="B9" s="2">
-        <v>101000132</v>
+        <v>101000123</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="3">
-        <v>1120011</v>
+        <v>2304070</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="2">
@@ -11812,7 +11813,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="3">
-        <v>1110001</v>
+        <v>2102020</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>16</v>
@@ -11820,13 +11821,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="B11" s="2">
-        <v>101001121</v>
+        <v>101001112</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="3">
-        <v>2102020</v>
+        <v>2102010</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>18</v>
@@ -11834,13 +11835,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="B12" s="2">
-        <v>101001122</v>
+        <v>101001121</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D12" s="3">
-        <v>2102010</v>
+        <v>2200010</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>20</v>
@@ -11848,31 +11849,32 @@
     </row>
     <row r="13" spans="1:6">
       <c r="B13" s="2">
-        <v>101001131</v>
+        <v>101001122</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="3">
-        <v>2200010</v>
+        <v>1120011</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" customFormat="1" spans="1:6">
       <c r="B14" s="2">
-        <v>101001132</v>
+        <v>101001123</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="3">
-        <v>1120011</v>
+        <v>2304070</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="F14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -122,6 +122,9 @@
     <t>增大技能范围</t>
   </si>
   <si>
+    <t>SkillPropertyAdd;1;2</t>
+  </si>
+  <si>
     <t>雷击</t>
   </si>
   <si>
@@ -134,16 +137,25 @@
     <t>命中后挂个灼烧Buff</t>
   </si>
   <si>
+    <t>BuffIdAdd;30204040</t>
+  </si>
+  <si>
     <t>寒霜</t>
   </si>
   <si>
     <t>命中后挂个减速Buff</t>
   </si>
   <si>
-    <t>恐惧</t>
+    <t>BuffIdAdd;11100012</t>
   </si>
   <si>
-    <t>命中后挂个恐惧Buff</t>
+    <t>恢复</t>
+  </si>
+  <si>
+    <t>使用技能时回口血</t>
+  </si>
+  <si>
+    <t>BuffInitIdAdd;40000010</t>
   </si>
   <si>
     <t>扩域2</t>
@@ -156,9 +168,6 @@
   </si>
   <si>
     <t>寒霜2</t>
-  </si>
-  <si>
-    <t>恐惧2</t>
   </si>
 </sst>
 </file>
@@ -11351,7 +11360,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{CEB8611B-D2B8-4B50-94D3-A462C68F57CD}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{8B25AD45-A264-4989-AACA-0E40194B4B34}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11736,7 +11745,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="2">
-        <v>101000111</v>
+        <v>111000111</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>15</v>
@@ -11747,70 +11756,81 @@
       <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="2">
-        <v>101000112</v>
+        <v>111000112</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="3">
         <v>2102010</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="2">
-        <v>101000121</v>
+        <v>111000121</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3">
         <v>2200010</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="2">
-        <v>101000122</v>
+        <v>111000122</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3">
         <v>1120011</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:6">
       <c r="B9" s="2">
-        <v>101000123</v>
+        <v>111000123</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3">
-        <v>2304070</v>
+        <v>2304030</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="2">
-        <v>101001111</v>
+        <v>111001111</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3">
         <v>2102020</v>
@@ -11821,58 +11841,58 @@
     </row>
     <row r="11" spans="1:6">
       <c r="B11" s="2">
-        <v>101001112</v>
+        <v>111001112</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D11" s="3">
         <v>2102010</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" s="2">
-        <v>101001121</v>
+        <v>111001121</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D12" s="3">
         <v>2200010</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" s="2">
-        <v>101001122</v>
+        <v>111001122</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3">
         <v>1120011</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:6">
       <c r="B14" s="2">
-        <v>101001123</v>
+        <v>111001123</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D14" s="3">
-        <v>2304070</v>
+        <v>2304030</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3"/>
     </row>

--- a/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillAugmentConfig.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -128,25 +128,28 @@
     <t>雷击</t>
   </si>
   <si>
-    <t>命中后电一下</t>
+    <t>追加一个技能</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;2200030</t>
   </si>
   <si>
     <t>灼烧</t>
   </si>
   <si>
-    <t>命中后挂个灼烧Buff</t>
+    <t>给对方挂个灼烧Buff</t>
   </si>
   <si>
     <t>BuffIdAdd;30204040</t>
   </si>
   <si>
-    <t>寒霜</t>
+    <t>眩晕</t>
   </si>
   <si>
-    <t>命中后挂个减速Buff</t>
+    <t>给对方挂个眩晕Buff</t>
   </si>
   <si>
-    <t>BuffIdAdd;11100012</t>
+    <t>BuffIdAdd;20000103</t>
   </si>
   <si>
     <t>恢复</t>
@@ -167,7 +170,7 @@
     <t>灼烧2</t>
   </si>
   <si>
-    <t>寒霜2</t>
+    <t>眩晕2</t>
   </si>
 </sst>
 </file>
@@ -11360,7 +11363,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{8B25AD45-A264-4989-AACA-0E40194B4B34}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{CE606ADE-704E-4BF9-A869-E1B0962184EC}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11773,22 +11776,25 @@
       <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="F6" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="2">
         <v>111000121</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3">
         <v>2200010</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -11796,16 +11802,16 @@
         <v>111000122</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3">
-        <v>1120011</v>
+        <v>2304070</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:6">
@@ -11813,16 +11819,16 @@
         <v>111000123</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="3">
         <v>2304030</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -11830,7 +11836,7 @@
         <v>111001111</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3">
         <v>2102020</v>
@@ -11838,13 +11844,16 @@
       <c r="E10" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="F10" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" s="2">
         <v>111001112</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3">
         <v>2102010</v>
@@ -11852,19 +11861,25 @@
       <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="F11" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" s="2">
         <v>111001121</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="3">
         <v>2200010</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -11872,13 +11887,16 @@
         <v>111001122</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="3">
-        <v>1120011</v>
+        <v>2304070</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:6">
@@ -11886,15 +11904,17 @@
         <v>111001123</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="3">
         <v>2304030</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
